--- a/Issues_No_Tests_final.xlsx
+++ b/Issues_No_Tests_final.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Issues" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,24 +27,17 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -53,13 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,31 +425,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U89"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="55" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -559,6 +536,7 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -587,6 +565,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>bug</t>
@@ -605,6 +584,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>The bug concerns incorrect computation of Gay-Berne interactions for special-bonded pairs, involving molecular simulation force-field behavior and incorrect energy/force/torque results, which requires domain-specific scientific knowledge to assess.</t>
@@ -647,6 +627,7 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -675,6 +656,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>bug
@@ -694,6 +676,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>The issue concerns missing rotational dynamics of granular rigid bodies in LAMMPS, involving physical concepts such as moments of inertia, units, and rigid-body motion.</t>
@@ -736,6 +719,7 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -764,6 +748,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>bug</t>
@@ -782,6 +767,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>The issue concerns incorrect thermodynamic behavior of a Langevin thermostat in molecular dynamics simulations, involving kinetic energy, temperature control, and degrees of freedom of rigid molecules.</t>
@@ -824,6 +810,7 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -852,6 +839,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>bug</t>
@@ -870,6 +858,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>The issue reports incorrect vector calculations in ellipsoid region surface code, involving mathematical formulas for contact distance vectors that are necessary to understand the bug.</t>
@@ -912,6 +901,7 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -940,6 +930,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>bug</t>
@@ -958,6 +949,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>The bug involves incorrect mathematical formulas for the ellipsoid region's surface geometry, which is necessary to understand the wall interaction failure.</t>
@@ -1000,6 +992,7 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -1028,6 +1021,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>bug</t>
@@ -1046,6 +1040,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>The issue reports incorrect total energy values in molecular dynamics simulations, which is a scientific numerical correctness problem requiring understanding of LAMMPS energy calculations and neighbor list behavior.</t>
@@ -1088,6 +1083,7 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -1116,6 +1112,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>bug</t>
@@ -1134,6 +1131,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>The issue describes incorrect force calculations and differing MD trajectories due to improper handling of pair style coefficients and cutoff symmetrization, which is domain-specific scientific behavior in molecular dynamics simulations.</t>
@@ -1176,6 +1174,7 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -1204,6 +1203,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>bug</t>
@@ -1222,6 +1222,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>The issue involves molecular dynamics simulation concepts such as rigid molecules, periodic boundary conditions, and minimum image conventions, which are necessary to understand the restart failure.</t>
@@ -1264,6 +1265,7 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -1292,6 +1294,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>bug</t>
@@ -1310,6 +1313,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>The issue involves incorrect mathematical formulation of the damping coefficient in cohesive DMT contact models, referencing equations and physical constants that lead to nan positions.</t>
@@ -1352,6 +1356,7 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -1380,6 +1385,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>bug</t>
@@ -1398,6 +1404,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>The bug concerns incorrect transformation of atomic positions and simulation cell vectors for triclinic systems in LAMMPS dump output, which involves domain-specific scientific concepts of lattice geometry and molecular simulation coordinate representation.</t>
@@ -1440,6 +1447,7 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -1468,6 +1476,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>enhancement</t>
@@ -1486,6 +1495,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>The issue discusses implementing QTPIE charge equilibration with external electric fields, involving electronegativity equations, unit conversions for electric field terms, and domain-specific chemistry/physics concepts.</t>
@@ -1528,6 +1538,7 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -1556,6 +1567,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>bug</t>
@@ -1574,6 +1586,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>[Manually added] Linked issue for lammps-4339; see Reasoning of the primary issue row for the shared scientific rationale.</t>
@@ -1616,6 +1629,7 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -1644,6 +1658,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>bug</t>
@@ -1662,6 +1677,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>The bug concerns incorrect physical volume calculation for particle insertion in granular simulations, which requires scientific/domain knowledge of units and geometry.</t>
@@ -1704,6 +1720,7 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -1732,6 +1749,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>bug</t>
@@ -1750,6 +1768,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>The issue describes incorrect stress tensor calculation in a granular simulation, involving physical concepts of forces and stress, which is a scientific correctness bug in the numerical method.</t>
@@ -1792,6 +1811,7 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -1820,6 +1840,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>bug</t>
@@ -1838,6 +1859,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>The issue reports incorrect simulation behavior (lost atoms) in a Lennard-Jones fluid under shear flow, which is a domain-specific scientific correctness bug in molecular dynamics.</t>
@@ -1880,6 +1902,7 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -1908,6 +1931,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>bug</t>
@@ -1926,6 +1950,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Diagnosing the incorrect molecule IDs in fix reaxff/species depends on understanding LAMMPS’s scientific neighbor/communication and molecule/species identification algorithms across MPI ranks, which is domain- and computation-specific.</t>
@@ -1968,6 +1993,7 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -1996,6 +2022,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>bug</t>
@@ -2014,6 +2041,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>The issue reports incorrect scientific output from fix reaxff/species, specifically average atomic positions and average charge being reported instead of center-of-mass positions and total charge, which involves domain-specific physical/chemical concepts.</t>
@@ -2056,6 +2084,7 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -2084,6 +2113,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>bug</t>
@@ -2102,6 +2132,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>The bug leads to incorrect scientific computations (forces/energies become zero) due to an error in neighbor-list construction/pruning logic and cutoff handling, which requires domain-specific numerical/algorithmic understanding.</t>
@@ -2144,6 +2175,7 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -2172,6 +2204,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>bug</t>
@@ -2190,6 +2223,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>The bug concerns incorrect coordination numbers from a radial distribution function calculation, which requires understanding of chemistry/domain-specific scientific concepts like coordination number and RDF.</t>
@@ -2232,6 +2266,7 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -2285,6 +2320,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>The issue discusses the incorrect implementation of a density lower limit rho0/10 in a fluid-solid interaction model, requiring domain knowledge of the RHEO method and physical unit systems.</t>
@@ -2327,6 +2363,7 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -2379,6 +2416,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>The issue describes incorrect scientific behavior in SRD shear flow simulation with fix deform and fix srd, and includes scientific velocity profile plots showing the kink and vanishing profile.</t>
@@ -2421,6 +2459,7 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -2449,6 +2488,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>bug</t>
@@ -2467,6 +2507,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>The issue describes differing simulation outputs for equivalent molecule files, involving reaction progress and molecular topology in LAMMPS, which is domain-specific scientific behavior.</t>
@@ -2509,6 +2550,7 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -2537,6 +2579,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>enhancement</t>
@@ -2555,6 +2598,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>The issue requests access to SHAKE constraint forces for computing potential mean force, which involves domain-specific molecular dynamics and constrained-bond scientific concepts.</t>
@@ -2597,6 +2641,7 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -2625,6 +2670,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>bug
@@ -2644,6 +2690,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>The bug involves incorrect Langevin thermostat force calculations due to velocity updates, which is domain-specific scientific/physics content.</t>
@@ -2686,6 +2733,7 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -2737,6 +2785,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>The issue reports incorrect SPH kernel gradient calculations and discusses color function/proportion formulations for phase interface identification, involving domain-specific scientific equations and numerical methods.</t>
@@ -2779,6 +2828,7 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -2807,6 +2857,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>bug</t>
@@ -2825,6 +2876,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>The issue concerns inconsistent physics of the GPU-accelerated core-shell model, involving Coulomb/Ewald sums, cutoff dependence, lattice parameters, and phase transition temperatures, which requires domain-specific scientific knowledge to understand.</t>
@@ -2867,6 +2919,7 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -2895,6 +2948,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>bug</t>
@@ -2913,6 +2967,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>The issue reports incorrect dipolar energy calculations between pair styles, requiring analytical dipolar formulas and spin configurations, and includes attached PDF plots of the test results.</t>
@@ -2988,6 +3043,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/920</t>
@@ -3001,6 +3058,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>The issue reports a discrepancy in potential energy calculations for a molecular dynamics simulation, involving numerical errors in nonbonded force components and discussion of PME and FFT algorithms, which are domain-specific scientific concepts.</t>
@@ -3076,6 +3134,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/1100</t>
@@ -3089,6 +3149,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>The issue discusses specific algorithms (SETTLE, CCMA) for handling molecular constraints in simulations, requiring scientific knowledge of molecular geometry and constraint satisfaction.</t>
@@ -3164,6 +3225,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>bug</t>
@@ -3182,6 +3244,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>The issue discusses numerical precision and implicit solvent model (GBn2) causing NaN energy during minimization, involving domain-specific scientific concepts like force calculations and energy minimization.</t>
@@ -3257,6 +3320,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/1592</t>
@@ -3270,6 +3335,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>The issue reports a numerical instability (nan particle coordinates) caused by GB (Generalized Born) forces in implicit solvent simulations, which involves domain-specific scientific knowledge about force fields and molecular dynamics.</t>
@@ -3345,6 +3411,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/1640</t>
@@ -3358,6 +3426,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>The issue discusses performance bottlenecks in GPU utilization for AMOEBA force field simulations, involving DIIS iterative solver, matrix inversion, SVD, and numerical precision concerns, which are domain-specific scientific computing topics.</t>
@@ -3433,6 +3502,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/1679</t>
@@ -3446,6 +3517,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>The issue discusses numerical precision and mathematical formulations of the velocity Verlet integrator in GHMC, focusing on floating-point representation and its impact on acceptance rates, which involves domain-specific scientific knowledge.</t>
@@ -3526,6 +3598,7 @@
           <t>https://cloud.githubusercontent.com/assets/19587267/20185625/140ef63a-a76d-11e6-9864-316234a4a2e4.png</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/1682</t>
@@ -3539,6 +3612,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>The issue involves numerical instability (NaN) in molecular dynamics simulations, requiring understanding of domain-specific concepts like triclinic box vectors, integrators, force fields, and PME parameters, which makes it a scientific bug.</t>
@@ -3614,6 +3688,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/1932</t>
@@ -3627,6 +3703,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>The issue involves domain-specific scientific knowledge about molecular topology, force fields, virtual sites, and coordinate assignment in molecular dynamics simulations, which is a scientific correctness concern.</t>
@@ -3702,6 +3779,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/2152</t>
@@ -3715,6 +3794,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>The issue involves scientific domain knowledge about force fields, polarizabilities, PME, and numerical precision in molecular dynamics simulations.</t>
@@ -3796,6 +3876,7 @@
 https://user-images.githubusercontent.com/3656088/52311687-d2705380-2975-11e9-84ce-0f51e42ba3fc.png</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/2257</t>
@@ -3809,6 +3890,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>The issue discusses numerical precision bugs in a scientific simulation context (NCMC, charge perturbation) and includes domain-specific plots comparing work distributions across precision levels.</t>
@@ -3884,6 +3966,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/2318</t>
@@ -3897,6 +3981,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>The issue discusses incorrect energy and force values due to handling of nonbonded exceptions with cutoff methods like PME and CutoffNonPeriodic, involving domain-specific scientific knowledge about electrostatics and numerical methods.</t>
@@ -3972,6 +4057,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/2322</t>
@@ -3985,6 +4072,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>The issue reports a bug in a molecular dynamics software where distance computation between centroid groups (a domain-specific concept) gives incorrect results under periodic boundary conditions, involving scientific accuracy and numerical methods.</t>
@@ -4060,6 +4148,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/2328</t>
@@ -4073,6 +4163,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>The issue reports different potential energies between CUDA and CPU platforms when using particle parameter offsets in OpenMM, which is a scientific computation error affecting physical correctness.</t>
@@ -4148,6 +4239,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>bug</t>
@@ -4166,6 +4258,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>The issue involves incorrect virtual site placement for lone pairs in the Drude-2013 forcefield, which is a domain-specific scientific algorithm causing a crash (NaN coordinates), and understanding the bug requires knowledge of molecular simulation forcefields.</t>
@@ -4241,6 +4334,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/2544</t>
@@ -4254,6 +4349,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>The issue involves an inconsistency in Lennard-Jones potential energy calculations across platforms due to mismatched nonbonded methods, requiring domain knowledge of molecular dynamics force fields and cutoff handling.</t>
@@ -4329,6 +4425,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>bug</t>
@@ -4347,6 +4444,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>The issue involves incorrect temperature calculation due to counting degrees of freedom with constraints between massless particles, which is a domain-specific thermodynamics and statistical mechanics problem.</t>
@@ -4422,6 +4520,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/2644</t>
@@ -4435,6 +4535,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>The issue involves a segmentation fault caused by numerical precision in CMAP torsion angle computation using fmod, a domain-specific scientific algorithm in molecular dynamics.</t>
@@ -4510,6 +4611,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>bug</t>
@@ -4528,6 +4630,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>The issue describes a bug where energy evaluations in molecular dynamics simulations return infinity (inf) due to a CUDA platform-specific problem, which involves domain-specific scientific knowledge about force fields and numerical accuracy in molecular simulations.</t>
@@ -4603,6 +4706,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>bug
@@ -4623,6 +4727,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>The issue involves molecular dynamics simulation solvation, energy minimization, and NaN results, which are domain-specific scientific concepts necessary to understand the bug.</t>
@@ -4698,6 +4803,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>enhancement</t>
@@ -4716,6 +4822,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>The issue involves a numerical singularity in the gradient of a custom potential function, which is a mathematical/domain-specific problem in molecular simulation force calculations.</t>
@@ -4815,6 +4922,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>The issue involves a bug in molecular simulation software where incorrect centering of a protein in a solvent box affects scientific correctness (type 1), and it includes scientific images showing the misalignment (type 2).</t>
@@ -4890,6 +4998,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/3280</t>
@@ -4903,6 +5013,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>The issue discusses convergence problems with long-range corrections in a custom nonbonded force using double exponential potentials, which involves numerical methods and domain-specific scientific concepts.</t>
@@ -4978,6 +5089,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/3311</t>
@@ -4991,6 +5104,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>The issue discusses a negative spring constant in harmonic bond forces used by the AMOEBA force field for Urey-Bradley terms, which is a domain-specific scientific concept.</t>
@@ -5066,6 +5180,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>bug</t>
@@ -5084,6 +5199,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>The issue discusses restricting scale factors for Lennard-Jones parameters (sigma, epsilon) in molecular dynamics free energy calculations, requiring domain-specific knowledge of alchemical transformations and force field parameter offsets.</t>
@@ -5159,6 +5275,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>bug</t>
@@ -5177,6 +5294,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>The issue discusses molecular dynamics force field parameters (sigma and epsilon in non-bonded interactions) and their physical correctness, which involves domain-specific scientific knowledge about potential functions and simulation stability.</t>
@@ -5275,6 +5393,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>The issue describes a molecular dynamics gentle equilibration protocol with domain-specific concepts (stages, restraint forces, CUDA errors in scientific simulation) and includes an image showing the equilibration protocol flowchart.</t>
@@ -5350,6 +5469,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/3460</t>
@@ -5363,6 +5484,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>The issue discusses perturbation of nonbonded parameters in a molecular dynamics simulation, involving domain-specific concepts like force fields, PME, and particle parameters, which are scientific in nature.</t>
@@ -5438,6 +5560,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>bug</t>
@@ -5456,6 +5579,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>The issue describes a discrepancy in computed kinetic energy values between different computing platforms for a Langevin integrator, which involves domain-specific scientific knowledge about molecular dynamics simulations and numerical methods.</t>
@@ -5531,6 +5655,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/3771</t>
@@ -5544,6 +5670,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>The issue describes incorrect potential energy calculations due to atom reordering in CUDA platform, which is a domain-specific scientific problem involving force fields and molecular mechanics.</t>
@@ -5619,6 +5746,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>bug</t>
@@ -5637,6 +5765,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>The issue involves a numerical error in force calculations due to evaluating 0^0 in an expression within CustomNonbondedForce and CustomBondForce, which is a domain-specific scientific computing problem related to molecular dynamics force fields.</t>
@@ -5712,6 +5841,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>bug</t>
@@ -5730,6 +5860,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>The issue describes a numerical precision problem in a scientific simulation integrator, specifically regarding energy conservation in NVE ensemble, which involves domain-specific scientific knowledge about precision and molecular dynamics.</t>
@@ -5805,6 +5936,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>bug</t>
@@ -5823,6 +5955,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>The issue involves domain-specific scientific knowledge about crystallographic waters and ion replacement in molecular simulations, and the bug affects the correctness of the solvent modeling process.</t>
@@ -5898,6 +6031,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/4119</t>
@@ -5911,6 +6046,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>The issue discusses incorrect molecular dynamics behavior (jumping molecules) due to a barostat implementation, requiring domain knowledge of MD algorithms and thermodynamics, and includes movie files showing molecular trajectories.</t>
@@ -5986,6 +6122,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/4148</t>
@@ -5999,6 +6137,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>The issue involves numerical instability in molecular dynamics simulations with DrudeLangevinIntegrator, harmonic bond energies, and interaction groups in custom nonbonded forces, which are domain-specific scientific concepts in computational chemistry.</t>
@@ -6074,6 +6213,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/4249</t>
@@ -6087,6 +6228,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>The issue reports incorrect numerical computation of energy parameter derivatives in a molecular simulation library, which is a domain-specific scientific correctness bug involving force field calculations.</t>
@@ -6162,6 +6304,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/4279</t>
@@ -6175,6 +6319,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>The issue involves domain-specific scientific knowledge about coarse-grained RNA nucleotide force field templates, patches for terminal modifications, and virtual sites, which are necessary to understand the bug.</t>
@@ -6256,6 +6401,7 @@
 https://github.com/openmm/openmm/assets/25778144/eb5b6b13-0784-4fbc-8b4a-94a2cf5b930a</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/4364</t>
@@ -6269,6 +6415,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>The issue involves unstable energies in NPT molecular dynamics, referencing specific algorithms (Langevin integrator, MonteCarlo barostat) and thermodynamic concepts, and includes scientific plots of potential energy and temperature that are central to demonstrating the bug.</t>
@@ -6344,6 +6491,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>enhancement</t>
@@ -6362,6 +6510,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>The issue discusses switching the discretization algorithm (LF-Middle) for Langevin integrators in a molecular dynamics library, which involves domain-specific numerical methods and mathematical formulations.</t>
@@ -6444,6 +6593,7 @@
 https://github.com/openmm/openmm/assets/33414534/267c83f2-d969-4775-82c6-9669cae41d2b</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/4618</t>
@@ -6457,6 +6607,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>The issue discusses incorrect potential energy and density from MonteCarloFlexibleBarostat, involving physics of barostat moves and numerical precision, and includes scientific plots of energy traces.</t>
@@ -6532,6 +6683,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/4748</t>
@@ -6545,6 +6698,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>The issue concerns the loss of Zn2+ ion representation during energy minimization in molecular dynamics simulations, involving domain-specific scientific knowledge about formal charges, force fields, and PDB file handling.</t>
@@ -6620,6 +6774,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/5069</t>
@@ -6633,6 +6789,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>The issue involves incorrect energy calculations in a molecular dynamics simulation, a domain-specific scientific concept.</t>
@@ -6708,6 +6865,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/5117</t>
@@ -6721,6 +6880,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>The issue concerns incorrect energy calculations (non-zero potential energy for a force group with zero bonds) in a molecular dynamics simulation, which is a domain-specific scientific problem involving numerical precision and force group handling.</t>
@@ -6796,6 +6956,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/5242</t>
@@ -6809,6 +6971,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>The issue discusses convergence failure in a local energy minimizer due to floating-point precision, involving numerical methods and domain-specific concepts like energy minimization and constraints in molecular dynamics.</t>
@@ -6884,6 +7047,8 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/5302</t>
@@ -6897,6 +7062,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>The issue involves incorrect handling of molecular connectivity and covalent maps in a molecular dynamics force field, leading to wrong simulation results, which is a domain-specific scientific bug.</t>
@@ -6982,6 +7148,7 @@
 https://github.com/user-attachments/assets/57e02e4b-00de-420b-9a37-628e4c603fc8</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>https://github.com/openmm/openmm/pull/5346</t>
@@ -6995,6 +7162,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>The issue discusses non-reproducible forces/energies in molecular simulation with PME and CustomCVForce, involving numerical precision and CUDA race conditions (type 1), and includes scientific plots of energy spread and force RMS deviation (type 2).</t>
@@ -7095,6 +7263,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>The issue involves molecular forcefield energy minimization, a domain-specific scientific concept, and includes screenshots of molecular structures and scientific output.</t>
@@ -7137,6 +7306,7 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -7165,6 +7335,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>enhancement</t>
@@ -7183,6 +7354,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>The feature request concerns the scientific/physical implementation of an electric-field coupling in REAXFF charge equilibration (QEq/QTPIE), including formulas and periodic-boundary/long-range charge-transfer behavior, which requires domain-specific numerical/scientific knowledge.</t>
@@ -7225,6 +7397,7 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -7253,6 +7426,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>bug</t>
@@ -7271,6 +7445,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>Fixing the hybrid/overlay argument parsing for dispersion/d3 vs the valid pair-style name “zero” requires domain-specific knowledge of LAMMPS pair-style argument partitioning logic.</t>
@@ -7313,6 +7488,7 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
@@ -7341,6 +7517,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>bug
@@ -7360,6 +7537,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>The bug produces incorrect (nan/garbage) thermodynamic/thermo output from a GPU-based hybrid short-range potential, which is a numerical/scientific correctness issue central to the simulation results.</t>
@@ -7402,22 +7580,23 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>543</v>
+        <v>4206</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Implement short neighborlists on manybody potentials in GPU package</t>
+          <t>[Feature Request] Implement adjustments to b2y and b2x used in the k_transpose kernel launch</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/543</t>
+          <t>https://github.com/lammps/lammps/issues/4206</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7430,6 +7609,7 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>enhancement
@@ -7438,20 +7618,21 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/597</t>
+          <t>https://github.com/lammps/lammps/pull/4319</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>597</v>
+        <v>4319</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Implementing short neighbor lists for GPU manybody potentials affects the cutoff-based neighbor construction and therefore the numerical correctness of the sw/vashishta/tersoff force calculations.</t>
+          <t>The bug’s fix depends on CUDA kernel launch configuration (block size) to avoid exceeding GPU block-count limits, which is tightly coupled to numerical kernel execution behavior and requires nontrivial technical reasoning beyond generic software issues.</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7481,7 +7662,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -7491,22 +7672,23 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4206</v>
+        <v>4365</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[Feature Request] Implement adjustments to b2y and b2x used in the k_transpose kernel launch</t>
+          <t>[BUG] Segmentation fault when computing PTM</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/4206</t>
+          <t>https://github.com/lammps/lammps/issues/4365</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7519,28 +7701,29 @@
           <t>No</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>enhancement
-gpu_package</t>
+          <t>bug</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/4319</t>
+          <t>https://github.com/lammps/lammps/pull/4370</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>4319</v>
+        <v>4370</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>The bug’s fix depends on CUDA kernel launch configuration (block size) to avoid exceeding GPU block-count limits, which is tightly coupled to numerical kernel execution behavior and requires nontrivial technical reasoning beyond generic software issues.</t>
+          <t>Diagnosing and fixing the segmentation fault requires understanding LAMMPS scientific compute internals (PTM/neighborhood/multi neighbor list stencil/memory usage) rather than generic software behavior.</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7560,12 +7743,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>swe_dominant</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -7575,268 +7758,273 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
+          <t>insufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>lammps/lammps</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>4338</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>[BUG]  GRANULAR package fix_pour: frequency of insertion not updated if timestep changed after defining fix_pour in input script</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://github.com/lammps/lammps/issues/4338</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://github.com/lammps/lammps/pull/4339</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>4339</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>The bug affects the numerical insertion frequency of particles in a granular simulation by mis-handling timestep-dependent scheduling, which directly impacts scientific computation results.</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Update: add another two PR-paired issues https://github.com/lammps/lammps/issues/4337 and https://github.com/lammps/lammps/issues/4216</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
           <t>sufficient</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="B80" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
         <is>
           <t>lammps/lammps</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>4365</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>[BUG] Segmentation fault when computing PTM</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>https://github.com/lammps/lammps/issues/4365</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
+      <c r="C81" t="n">
+        <v>4151</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>[BUG] Inconsistent syntax for dump_modify triclinic/general</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://github.com/lammps/lammps/issues/4151</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
         <is>
           <t>bug</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>https://github.com/lammps/lammps/pull/4370</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
-        <v>4370</v>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>Diagnosing and fixing the segmentation fault requires understanding LAMMPS scientific compute internals (PTM/neighborhood/multi neighbor list stencil/memory usage) rather than generic software behavior.</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://github.com/lammps/lammps/pull/4152</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>4152</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>The bug concerns the parsing/semantic handling of the dump_modify triclinic/general option specifically affecting how triclinic/general simulation box geometry is interpreted in dump outputs, which is central scientific-software behavior.</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
         <is>
           <t>Materials Science</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>swe_dominant</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
         <is>
           <t>insufficient</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>lammps/lammps</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>4338</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>[BUG]  GRANULAR package fix_pour: frequency of insertion not updated if timestep changed after defining fix_pour in input script</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>https://github.com/lammps/lammps/issues/4338</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>biopython/biopython</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>3757</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Parsing Exonerate text output with SearchIO does not assign target strand correctly</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://github.com/biopython/biopython/issues/3757</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>https://github.com/lammps/lammps/pull/4339</t>
-        </is>
-      </c>
-      <c r="K81" t="n">
-        <v>4339</v>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>The bug affects the numerical insertion frequency of particles in a granular simulation by mis-handling timestep-dependent scheduling, which directly impacts scientific computation results.</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>Update</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Update: add another two PR-paired issues https://github.com/lammps/lammps/issues/4337 and https://github.com/lammps/lammps/issues/4216</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>Materials Science</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://github.com/biopython/biopython/pull/3761</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>3761</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Correctly parsing biological strand orientation from Exonerate text output into SearchIO hit_strand_all is a domain-specific scientific-data interpretation/algorithmic bug.</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Bioinformatics</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
         <is>
           <t>swe_dominant</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>sufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>lammps/lammps</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>4151</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>[BUG] Inconsistent syntax for dump_modify triclinic/general</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>https://github.com/lammps/lammps/issues/4151</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>https://github.com/lammps/lammps/pull/4152</t>
-        </is>
-      </c>
-      <c r="K82" t="n">
-        <v>4152</v>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>The bug concerns the parsing/semantic handling of the dump_modify triclinic/general option specifically affecting how triclinic/general simulation box geometry is interpreted in dump outputs, which is central scientific-software behavior.</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>Materials Science</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>swe_dominant</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>insufficient</t>
@@ -7844,27 +8032,28 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>biopython/biopython</t>
+          <t>qgis/QGIS</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3757</v>
+        <v>63868</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Parsing Exonerate text output with SearchIO does not assign target strand correctly</t>
+          <t>Concave Hull algorithm generates empty geometry</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://github.com/biopython/biopython/issues/3757</t>
+          <t>https://github.com/qgis/QGIS/issues/63868</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7872,202 +8061,215 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>https://github.com/biopython/biopython/pull/3761</t>
-        </is>
-      </c>
-      <c r="K83" t="n">
-        <v>3761</v>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>Correctly parsing biological strand orientation from Exonerate text output into SearchIO hit_strand_all is a domain-specific scientific-data interpretation/algorithmic bug.</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>Bioinformatics</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>swe_dominant</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>insufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>qgis/QGIS</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>63868</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Concave Hull algorithm generates empty geometry</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>https://github.com/qgis/QGIS/issues/63868</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
         <is>
           <t>Processing
 Bug
 geos</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>https://github.com/qgis/QGIS/pull/64781</t>
         </is>
       </c>
-      <c r="K84" t="n">
+      <c r="K83" t="n">
         <v>64781</v>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
         <is>
           <t>The bug concerns a computational geometry algorithm (concave hull) interacting with GEOS triangulation producing an empty/failed hull from specific coordinate configurations, requiring numerical/scientific understanding of geometric algorithms and robustness.</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>swe_dominant</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
         <is>
           <t>insufficient</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
         <is>
           <t>astropy/astropy</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="C84" t="n">
         <v>16372</v>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>Faster checksum implementation</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>https://github.com/astropy/astropy/issues/16372</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
         <is>
           <t>Feature Request
 io.fits
 Performance</t>
         </is>
       </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>https://github.com/astropy/astropy/pull/17209</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>17209</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>This feature request is about optimizing the FITS checksum/datasum calculation algorithm for scientific file integrity, where correctness of the checksum implementation is mathematically/algorithmically central.</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Astronomy</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>qutip/qutip</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1919</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Dicke Entropy returns -Inf</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://github.com/qutip/qutip/issues/1919</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>good first issue</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>https://github.com/astropy/astropy/pull/17209</t>
+          <t>https://github.com/qutip/qutip/pull/2466</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>17209</v>
+        <v>2466</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>This feature request is about optimizing the FITS checksum/datasum calculation algorithm for scientific file integrity, where correctness of the checksum implementation is mathematically/algorithmically central.</t>
+          <t>The bug is due to numerical issues in computing eigenvalues and entropy (negative values leading to -Inf), requiring scientific/numerical expertise to diagnose and fix correctly.</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8082,7 +8284,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -8102,427 +8304,185 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
+          <t>sufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>qutip/qutip</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1128</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Husimi Q and Wigner spin functions don't give correct results</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://github.com/qutip/qutip/issues/1128</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>physics</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>https://github.com/qutip/qutip/pull/1195</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>The bug reports incorrect scientific results for Husimi Q and Wigner spin functions and traces the error to a mathematical factor/order and spin-coherent state implementation, requiring domain-specific physics/numerical knowledge to diagnose and fix.</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>deepchem/deepchem</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2126</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Errors while calculating `vina_energy_term`</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://github.com/deepchem/deepchem/issues/2126</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>https://github.com/deepchem/deepchem/pull/2132</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>2132</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>The bug concerns numerical tensor shape handling in the `vina_energy_term`/`weighted_linear_sum` calculation and incorrect math implementation for general `M` values, which is central scientific computation logic.</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
           <t>insufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>qutip/qutip</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>1919</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Dicke Entropy returns -Inf</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>https://github.com/qutip/qutip/issues/1919</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>good first issue</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>https://github.com/qutip/qutip/pull/2466</t>
-        </is>
-      </c>
-      <c r="K86" t="n">
-        <v>2466</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>The bug is due to numerical issues in computing eigenvalues and entropy (negative values leading to -Inf), requiring scientific/numerical expertise to diagnose and fix correctly.</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>swe_dominant</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>sufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>qutip/qutip</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>1128</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Husimi Q and Wigner spin functions don't give correct results</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>https://github.com/qutip/qutip/issues/1128</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>physics</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>https://github.com/qutip/qutip/pull/1195</t>
-        </is>
-      </c>
-      <c r="K87" t="n">
-        <v>1195</v>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>The bug reports incorrect scientific results for Husimi Q and Wigner spin functions and traces the error to a mathematical factor/order and spin-coherent state implementation, requiring domain-specific physics/numerical knowledge to diagnose and fix.</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>joint</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>sufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>deepchem/deepchem</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>2126</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Errors while calculating `vina_energy_term`</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>https://github.com/deepchem/deepchem/issues/2126</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>https://github.com/deepchem/deepchem/pull/2132</t>
-        </is>
-      </c>
-      <c r="K88" t="n">
-        <v>2132</v>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>The bug concerns numerical tensor shape handling in the `vina_energy_term`/`weighted_linear_sum` calculation and incorrect math implementation for general `M` values, which is central scientific computation logic.</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>swe_dominant</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>insufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>deepchem/deepchem</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>1716</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>use_chirality in WeaveFeaturizer</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>https://github.com/deepchem/deepchem/issues/1716</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>bug
-Contribution Welcome</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>https://github.com/deepchem/deepchem/pull/1769</t>
-        </is>
-      </c>
-      <c r="K89" t="n">
-        <v>1769</v>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>The bug involves a domain-specific graph-featurization parameter (bond/traversal length) whose correct behavior depends on how chirality features change feature dimensionality.</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>swe_dominant</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>sufficient</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Update</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>openmm__openmm-3872 was decided 'Pass' in review but has no matching row in either source xlsx; excluded per user instruction.</t>
         </is>
       </c>
     </row>
